--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555781.6479232884</v>
+        <v>555782</v>
       </c>
       <c r="R2" t="n">
-        <v>6696842.323452283</v>
+        <v>6696842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93030</v>
+        <v>93032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93032</v>
+        <v>93036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93036</v>
+        <v>93049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93049</v>
+        <v>93050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93050</v>
+        <v>93051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93051</v>
+        <v>93060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93084</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97329446</v>
+        <v>129080521</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,52 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555780.0583261261</v>
+        <v>555798</v>
       </c>
       <c r="R3" t="n">
-        <v>6696881.340733854</v>
+        <v>6696849</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,72 +863,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97329335</v>
+        <v>129080506</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555780.0583261261</v>
+        <v>555779</v>
       </c>
       <c r="R4" t="n">
-        <v>6696881.340733854</v>
+        <v>6696887</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,63 +967,68 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97328867</v>
+        <v>97329307</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555753.1368644732</v>
+        <v>555780</v>
       </c>
       <c r="R5" t="n">
-        <v>6696893.776213734</v>
+        <v>6696881</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,33 +1079,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97329167</v>
+        <v>124288656</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,38 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555826.8146765307</v>
+        <v>555769</v>
       </c>
       <c r="R6" t="n">
-        <v>6696898.862166425</v>
+        <v>6696795</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,22 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97328938</v>
+        <v>129080508</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,38 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555780.4910950072</v>
+        <v>555770</v>
       </c>
       <c r="R7" t="n">
-        <v>6696853.178092062</v>
+        <v>6696857</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97328750</v>
+        <v>129080509</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,38 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555725.2940785955</v>
+        <v>555776</v>
       </c>
       <c r="R8" t="n">
-        <v>6696901.749964267</v>
+        <v>6696866</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,22 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97328832</v>
+        <v>129080512</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,38 +1400,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555779.2203884723</v>
+        <v>555776</v>
       </c>
       <c r="R9" t="n">
-        <v>6696871.44392027</v>
+        <v>6696786</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,54 +1486,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97329169</v>
+        <v>129080491</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555826.8146765307</v>
+        <v>555770</v>
       </c>
       <c r="R10" t="n">
-        <v>6696898.862166425</v>
+        <v>6696850</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,22 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,49 +1583,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97328720</v>
+        <v>97328741</v>
       </c>
       <c r="B11" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1744,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555718.9818685917</v>
+        <v>555721</v>
       </c>
       <c r="R11" t="n">
-        <v>6696893.745966963</v>
+        <v>6696895</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1779,7 +1654,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1664,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,15 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97328741</v>
+        <v>97328747</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555720.9462597554</v>
+        <v>555725</v>
       </c>
       <c r="R12" t="n">
-        <v>6696894.764509278</v>
+        <v>6696902</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,15 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97329314</v>
+        <v>97328938</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555818.1953765308</v>
+        <v>555781</v>
       </c>
       <c r="R13" t="n">
-        <v>6696879.950192579</v>
+        <v>6696853</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2005,7 +1870,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +1880,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,53 +1907,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97328989</v>
+        <v>97329167</v>
       </c>
       <c r="B14" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555813.2464571904</v>
+        <v>555827</v>
       </c>
       <c r="R14" t="n">
-        <v>6696879.87409499</v>
+        <v>6696899</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2120,7 +1978,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +1988,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,7 +1997,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2158,61 +2015,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97401155</v>
+        <v>97329314</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555773.8814013347</v>
+        <v>555818</v>
       </c>
       <c r="R15" t="n">
-        <v>6696832.320069506</v>
+        <v>6696879</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,22 +2081,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,77 +2111,58 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97401158</v>
+        <v>97329335</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555814.0235234372</v>
+        <v>555780</v>
       </c>
       <c r="R16" t="n">
-        <v>6696893.723520528</v>
+        <v>6696881</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2366,22 +2189,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,63 +2231,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97401037</v>
+        <v>124288644</v>
       </c>
       <c r="B17" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555790.6029287559</v>
+        <v>555774</v>
       </c>
       <c r="R17" t="n">
-        <v>6696871.618847977</v>
+        <v>6696769</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,22 +2296,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,75 +2316,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97413040</v>
+        <v>124288645</v>
       </c>
       <c r="B18" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555813.1552940429</v>
+        <v>555769</v>
       </c>
       <c r="R18" t="n">
-        <v>6696885.803047111</v>
+        <v>6696795</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2610,22 +2393,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,72 +2413,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97412989</v>
+        <v>129080493</v>
       </c>
       <c r="B19" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555816.6336634106</v>
+        <v>555776</v>
       </c>
       <c r="R19" t="n">
-        <v>6696852.745265569</v>
+        <v>6696784</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,29 +2490,19 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2759,80 +2510,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97412931</v>
+        <v>129080494</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555817.5778696365</v>
+        <v>555786</v>
       </c>
       <c r="R20" t="n">
-        <v>6696855.724984788</v>
+        <v>6696881</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2856,22 +2587,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,27 +2607,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97412958</v>
+        <v>129080496</v>
       </c>
       <c r="B21" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,48 +2630,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555808.6697553289</v>
+        <v>555738</v>
       </c>
       <c r="R21" t="n">
-        <v>6696855.5880158</v>
+        <v>6696882</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2979,22 +2684,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,27 +2704,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97329307</v>
+        <v>124288654</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,48 +2727,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555780.0583261261</v>
+        <v>555776</v>
       </c>
       <c r="R22" t="n">
-        <v>6696881.340733854</v>
+        <v>6696789</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3102,22 +2781,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,34 +2795,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124288644</v>
+        <v>129080504</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3161,21 +2824,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3185,10 +2848,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555774</v>
+        <v>555776</v>
       </c>
       <c r="R23" t="n">
-        <v>6696769</v>
+        <v>6696786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3215,12 +2878,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,19 +2910,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124288654</v>
+        <v>129080505</v>
       </c>
       <c r="B24" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3272,12 +2930,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3287,10 +2945,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555776</v>
+        <v>555779</v>
       </c>
       <c r="R24" t="n">
-        <v>6696789</v>
+        <v>6696888</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3317,12 +2975,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3349,10 +3007,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129080492</v>
+        <v>97328989</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3360,37 +3018,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555785</v>
+        <v>555814</v>
       </c>
       <c r="R25" t="n">
-        <v>6696895</v>
+        <v>6696880</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,12 +3075,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,6 +3099,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3446,48 +3118,58 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129080512</v>
+        <v>97401037</v>
       </c>
       <c r="B26" t="n">
-        <v>91879</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555776</v>
+        <v>555790</v>
       </c>
       <c r="R26" t="n">
-        <v>6696786</v>
+        <v>6696872</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,12 +3193,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,60 +3223,70 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129080494</v>
+        <v>97413040</v>
       </c>
       <c r="B27" t="n">
-        <v>91581</v>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555786</v>
+        <v>555813</v>
       </c>
       <c r="R27" t="n">
-        <v>6696881</v>
+        <v>6696885</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3608,12 +3310,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,44 +3340,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129080505</v>
+        <v>129080502</v>
       </c>
       <c r="B28" t="n">
-        <v>92034</v>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3675,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555779</v>
+        <v>555799</v>
       </c>
       <c r="R28" t="n">
-        <v>6696888</v>
+        <v>6696929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3737,54 +3449,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129080517</v>
+        <v>129080503</v>
       </c>
       <c r="B29" t="n">
-        <v>92899</v>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555773</v>
+        <v>555761</v>
       </c>
       <c r="R29" t="n">
-        <v>6696900</v>
+        <v>6696908</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3843,51 +3546,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129080521</v>
+        <v>97329169</v>
       </c>
       <c r="B30" t="n">
-        <v>86920</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>442</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555798</v>
+        <v>555827</v>
       </c>
       <c r="R30" t="n">
-        <v>6696849</v>
+        <v>6696899</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,17 +3612,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3636,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3949,32 +3654,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129080504</v>
+        <v>129080492</v>
       </c>
       <c r="B31" t="n">
-        <v>92034</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3984,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555776</v>
+        <v>555785</v>
       </c>
       <c r="R31" t="n">
-        <v>6696786</v>
+        <v>6696895</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,48 +3751,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129080496</v>
+        <v>97328738</v>
       </c>
       <c r="B32" t="n">
-        <v>91581</v>
+        <v>91282</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555738</v>
+        <v>555766</v>
       </c>
       <c r="R32" t="n">
-        <v>6696882</v>
+        <v>6696860</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4111,42 +3819,53 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129080508</v>
+        <v>97328720</v>
       </c>
       <c r="B33" t="n">
-        <v>91879</v>
+        <v>93233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4154,37 +3873,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555770</v>
+        <v>555719</v>
       </c>
       <c r="R33" t="n">
-        <v>6696857</v>
+        <v>6696894</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,12 +3937,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129080509</v>
+        <v>97328867</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>93233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,37 +3990,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555776</v>
+        <v>555753</v>
       </c>
       <c r="R34" t="n">
-        <v>6696866</v>
+        <v>6696894</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,12 +4045,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4337,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129080499</v>
+        <v>97329113</v>
       </c>
       <c r="B35" t="n">
-        <v>57890</v>
+        <v>93233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,42 +4098,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555799</v>
+        <v>555787</v>
       </c>
       <c r="R35" t="n">
-        <v>6696875</v>
+        <v>6696933</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4407,12 +4162,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,10 +4204,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129080493</v>
+        <v>129080517</v>
       </c>
       <c r="B36" t="n">
-        <v>91581</v>
+        <v>93233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4450,34 +4215,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555776</v>
+        <v>555773</v>
       </c>
       <c r="R36" t="n">
-        <v>6696784</v>
+        <v>6696900</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4536,45 +4310,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129080503</v>
+        <v>129080518</v>
       </c>
       <c r="B37" t="n">
-        <v>92875</v>
+        <v>93233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555761</v>
+        <v>555789</v>
       </c>
       <c r="R37" t="n">
-        <v>6696908</v>
+        <v>6696889</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4633,14 +4416,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129080518</v>
+        <v>129080519</v>
       </c>
       <c r="B38" t="n">
-        <v>92899</v>
+        <v>93233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4663,7 +4446,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4677,10 +4460,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555789</v>
+        <v>555840</v>
       </c>
       <c r="R38" t="n">
-        <v>6696889</v>
+        <v>6696854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4739,10 +4522,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129080506</v>
+        <v>97328790</v>
       </c>
       <c r="B39" t="n">
-        <v>92224</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,37 +4533,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555779</v>
+        <v>555770</v>
       </c>
       <c r="R39" t="n">
-        <v>6696887</v>
+        <v>6696842</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4804,12 +4588,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4833,6 +4627,1498 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>97328832</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>555779</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6696871</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>97329051</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555791</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6696931</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>97412958</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>555808</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6696856</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>97412989</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>555816</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6696852</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129080498</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>555757</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6696784</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129080499</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>555799</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6696875</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>97329094</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>555780</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6696881</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>97329266</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>555847</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6696871</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>97401155</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>555774</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6696832</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>97401158</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>555814</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6696894</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>97401177</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>555755</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6696820</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>97412931</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>555818</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6696855</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>97328646</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>555766</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6696860</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1453-2026 artfynd.xlsx
+++ b/artfynd/A 1453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75467725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288656</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080491</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328741</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328747</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328938</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2012,6 +2077,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329167</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329314</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329335</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288644</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288645</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080493</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080494</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080496</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288654</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2907,6 +3017,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080504</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080505</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328989</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3349,6 +3479,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97413040</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3446,6 +3581,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080502</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3543,6 +3683,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080503</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3651,6 +3796,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329169</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3748,6 +3898,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080492</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,6 +4014,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328738</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3976,6 +4136,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328720</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4084,6 +4249,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328867</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4201,6 +4371,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329113</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4307,6 +4482,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080517</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4413,6 +4593,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080518</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4519,6 +4704,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080519</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4627,6 +4817,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328790</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4735,6 +4930,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328832</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4843,6 +5043,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329051</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4961,6 +5166,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412958</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5075,6 +5285,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412989</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5177,6 +5392,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080498</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5279,6 +5499,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080499</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5401,6 +5626,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329094</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5519,6 +5749,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329266</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5637,6 +5872,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401155</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5759,6 +5999,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401158</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5877,6 +6122,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401177</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5999,6 +6249,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412931</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6119,8 +6374,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>